--- a/erp-server/erp-server-plm/src/main/resources/excel/exportProductPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/exportProductPlan.xlsx
@@ -36,13 +36,13 @@
     <t>产品款品</t>
   </si>
   <si>
-    <t>新品/老品</t>
+    <t>新品/老品升级</t>
   </si>
   <si>
     <t>三代规划（721原则）</t>
   </si>
   <si>
-    <t>产品名称</t>
+    <t>产品名称（中文）</t>
   </si>
   <si>
     <t>产品名称（英文）</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/exportProductPlan.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/exportProductPlan.xlsx
@@ -237,7 +237,7 @@
     <t>{.spuNo}</t>
   </si>
   <si>
-    <t>{.skuQty}</t>
+    <t>{.skuQtyStr}</t>
   </si>
   <si>
     <t>{.specification}</t>
